--- a/data/dividends_info_20260327.xlsx
+++ b/data/dividends_info_20260327.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K70"/>
+  <dimension ref="A1:K129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,11 +491,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.06</v>
+        <v>0.7</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -504,12 +504,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2027-02-22</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2027-02-24</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -519,30 +519,30 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>IT0005337818</t>
+          <t>IT0001031084</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>9</v>
+        <v>50.75</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6666666666666666</v>
+        <v>1.379310344827586</v>
       </c>
       <c r="J2" t="n">
-        <v>262</v>
+        <v>332</v>
       </c>
       <c r="K2" t="n">
-        <v>264</v>
+        <v>334</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.077</v>
+        <v>0.06</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -551,12 +551,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -566,30 +566,30 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>IT0001469383</t>
+          <t>IT0005337818</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.983999967575073</v>
+        <v>8.960000038146973</v>
       </c>
       <c r="I3" t="n">
-        <v>3.88104845052556</v>
+        <v>0.6696428542918696</v>
       </c>
       <c r="J3" t="n">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="K3" t="n">
-        <v>243</v>
+        <v>264</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.25</v>
+        <v>0.077</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -598,45 +598,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Straordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>IT0001207098</t>
+          <t>IT0001469383</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>21.97999954223633</v>
+        <v>1.968000054359436</v>
       </c>
       <c r="I4" t="n">
-        <v>1.137397657900789</v>
+        <v>3.912601517943693</v>
       </c>
       <c r="J4" t="n">
-        <v>87</v>
+        <v>241</v>
       </c>
       <c r="K4" t="n">
-        <v>89</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.195</v>
+        <v>0.2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -645,45 +645,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>IT0005331019</t>
+          <t>IT0005312027</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>21.89999961853027</v>
+        <v>5.449999809265137</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8904109744139194</v>
+        <v>3.669724899072381</v>
       </c>
       <c r="J5" t="n">
-        <v>87</v>
+        <v>234</v>
       </c>
       <c r="K5" t="n">
-        <v>89</v>
+        <v>236</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.29</v>
+        <v>0.26</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -692,12 +692,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -707,30 +707,30 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>IT0005176406</t>
+          <t>IT0003128367</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>5.119999885559082</v>
+        <v>9.145999908447266</v>
       </c>
       <c r="I6" t="n">
-        <v>5.664062626601665</v>
+        <v>2.842772825307635</v>
       </c>
       <c r="J6" t="n">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="K6" t="n">
-        <v>89</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.16</v>
+        <v>0.376</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -739,12 +739,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -754,30 +754,30 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>IT0001250932</t>
+          <t>IT0000214293</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>3.944000005722046</v>
+        <v>17.89999961853027</v>
       </c>
       <c r="I7" t="n">
-        <v>4.056795125960151</v>
+        <v>2.100558703983215</v>
       </c>
       <c r="J7" t="n">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="K7" t="n">
-        <v>89</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1386</v>
+        <v>0.12</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -801,30 +801,30 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>IT0003027817</t>
+          <t>IT0004053440</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2.434000015258789</v>
+        <v>4.945000171661377</v>
       </c>
       <c r="I8" t="n">
-        <v>5.69433028476229</v>
+        <v>2.426693545688664</v>
       </c>
       <c r="J8" t="n">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="K8" t="n">
-        <v>89</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.63</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -833,12 +833,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -848,30 +848,30 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>IT0003856405</t>
+          <t>IT0001382024</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>58.58000183105469</v>
+        <v>2.119999885559082</v>
       </c>
       <c r="I9" t="n">
-        <v>1.075452339207715</v>
+        <v>4.009434178699683</v>
       </c>
       <c r="J9" t="n">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="K9" t="n">
-        <v>89</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.78</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -880,12 +880,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -895,30 +895,30 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>IT0005353815</t>
+          <t>IT0005561441</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>4.588235294117647</v>
+        <v>1.75</v>
       </c>
       <c r="J10" t="n">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="K10" t="n">
-        <v>89</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.85</v>
+        <v>0.15</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -927,12 +927,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -942,30 +942,30 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>IT0003796171</t>
+          <t>IT0004195308</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>19.78000068664551</v>
+        <v>30.29999923706055</v>
       </c>
       <c r="I11" t="n">
-        <v>4.297269820490342</v>
+        <v>0.4950495174156042</v>
       </c>
       <c r="J11" t="n">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="K11" t="n">
-        <v>89</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1813</v>
+        <v>0.25</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -984,19 +984,19 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Straordinario</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>IT0003153415</t>
+          <t>IT0001207098</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>6.326000213623047</v>
+        <v>21.8799991607666</v>
       </c>
       <c r="I12" t="n">
-        <v>2.865949950642908</v>
+        <v>1.142596021887785</v>
       </c>
       <c r="J12" t="n">
         <v>87</v>
@@ -1008,11 +1008,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.26</v>
+        <v>0.195</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1036,14 +1036,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>IT0003153621</t>
+          <t>IT0005331019</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>7.78000020980835</v>
+        <v>21.5</v>
       </c>
       <c r="I13" t="n">
-        <v>3.341902223501415</v>
+        <v>0.9069767441860466</v>
       </c>
       <c r="J13" t="n">
         <v>87</v>
@@ -1055,11 +1055,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.277</v>
+        <v>0.29</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1083,14 +1083,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>IT0003242622</t>
+          <t>IT0005176406</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>9.47599983215332</v>
+        <v>5.125</v>
       </c>
       <c r="I14" t="n">
-        <v>2.923174386940177</v>
+        <v>5.658536585365853</v>
       </c>
       <c r="J14" t="n">
         <v>87</v>
@@ -1102,11 +1102,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.11</v>
+        <v>0.16</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1115,12 +1115,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1130,30 +1130,30 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>NL0015000K93</t>
+          <t>IT0001250932</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>25.45000076293945</v>
+        <v>3.901999950408936</v>
       </c>
       <c r="I15" t="n">
-        <v>4.361492993023377</v>
+        <v>4.100461354009801</v>
       </c>
       <c r="J15" t="n">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="K15" t="n">
-        <v>97</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.03</v>
+        <v>0.1386</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1177,30 +1177,30 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>IT0001237053</t>
+          <t>IT0003027817</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.828000009059906</v>
+        <v>2.414000034332275</v>
       </c>
       <c r="I16" t="n">
-        <v>3.623188366152481</v>
+        <v>5.741507789097338</v>
       </c>
       <c r="J16" t="n">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="K16" t="n">
-        <v>68</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.023</v>
+        <v>0.63</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1224,30 +1224,30 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>IT0000060886</t>
+          <t>IT0003856405</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.4720000028610229</v>
+        <v>56.61999893188477</v>
       </c>
       <c r="I17" t="n">
-        <v>4.872881326395285</v>
+        <v>1.112681052427969</v>
       </c>
       <c r="J17" t="n">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="K17" t="n">
-        <v>68</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.18</v>
+        <v>0.78</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1271,30 +1271,30 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>IT0004329733</t>
+          <t>IT0005353815</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2.509999990463257</v>
+        <v>17</v>
       </c>
       <c r="I18" t="n">
-        <v>7.171314768283262</v>
+        <v>4.588235294117647</v>
       </c>
       <c r="J18" t="n">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="K18" t="n">
-        <v>61</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.25</v>
+        <v>0.85</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1318,30 +1318,30 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>IT0005453250</t>
+          <t>IT0003796171</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>12.1899995803833</v>
+        <v>19.79500007629395</v>
       </c>
       <c r="I19" t="n">
-        <v>2.050861432368802</v>
+        <v>4.294013623258032</v>
       </c>
       <c r="J19" t="n">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="K19" t="n">
-        <v>61</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.15</v>
+        <v>0.1813</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1365,30 +1365,30 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>IT0005275778</t>
+          <t>IT0003153415</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>3.579999923706055</v>
+        <v>6.381999969482422</v>
       </c>
       <c r="I20" t="n">
-        <v>4.189944223370775</v>
+        <v>2.840802269930179</v>
       </c>
       <c r="J20" t="n">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="K20" t="n">
-        <v>61</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.58</v>
+        <v>0.26</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1397,12 +1397,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1412,30 +1412,30 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>IT0001042610</t>
+          <t>IT0003153621</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>13.35000038146973</v>
+        <v>7.570000171661377</v>
       </c>
       <c r="I21" t="n">
-        <v>4.344569164245573</v>
+        <v>3.434610225945849</v>
       </c>
       <c r="J21" t="n">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="K21" t="n">
-        <v>61</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.104</v>
+        <v>0.277</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1444,12 +1444,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1459,30 +1459,30 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>IT0001233417</t>
+          <t>IT0003242622</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2.371999979019165</v>
+        <v>9.562000274658203</v>
       </c>
       <c r="I22" t="n">
-        <v>4.384485704886243</v>
+        <v>2.896883413966452</v>
       </c>
       <c r="J22" t="n">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="K22" t="n">
-        <v>54</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.29</v>
+        <v>1.11</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1491,12 +1491,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1506,30 +1506,30 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>IT0004056880</t>
+          <t>NL0015000K93</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>8.996000289916992</v>
+        <v>25.25</v>
       </c>
       <c r="I23" t="n">
-        <v>3.223654853869239</v>
+        <v>4.396039603960396</v>
       </c>
       <c r="J23" t="n">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="K23" t="n">
-        <v>54</v>
+        <v>97</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.64</v>
+        <v>0.03</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1538,12 +1538,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1553,30 +1553,30 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>IT0000062072</t>
+          <t>IT0001237053</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>33.75</v>
+        <v>0.8220000267028809</v>
       </c>
       <c r="I24" t="n">
-        <v>4.859259259259259</v>
+        <v>3.649634917937024</v>
       </c>
       <c r="J24" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="K24" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.432</v>
+        <v>0.023</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1600,30 +1600,30 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>IT0005211237</t>
+          <t>IT0000060886</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>9.835000038146973</v>
+        <v>0.460999995470047</v>
       </c>
       <c r="I25" t="n">
-        <v>4.392475834513507</v>
+        <v>4.98915406204042</v>
       </c>
       <c r="J25" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="K25" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.44</v>
+        <v>0.18</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1632,12 +1632,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1647,30 +1647,30 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>IT0005541336</t>
+          <t>IT0004329733</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>25.57999992370605</v>
+        <v>2.525000095367432</v>
       </c>
       <c r="I26" t="n">
-        <v>1.72009382842974</v>
+        <v>7.128712602040787</v>
       </c>
       <c r="J26" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="K26" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.47</v>
+        <v>0.25</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1679,12 +1679,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1694,30 +1694,30 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>IT0003428445</t>
+          <t>IT0005453250</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>7.269999980926514</v>
+        <v>12.1899995803833</v>
       </c>
       <c r="I27" t="n">
-        <v>6.464924363591286</v>
+        <v>2.050861432368802</v>
       </c>
       <c r="J27" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="K27" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.4</v>
+        <v>0.15</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1741,30 +1741,30 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>IT0004965148</t>
+          <t>IT0005275778</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>51.45999908447266</v>
+        <v>3.579999923706055</v>
       </c>
       <c r="I28" t="n">
-        <v>2.720559706388395</v>
+        <v>4.189944223370775</v>
       </c>
       <c r="J28" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="K28" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.3</v>
+        <v>0.58</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1773,12 +1773,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1788,30 +1788,30 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>IT0005366767</t>
+          <t>IT0001042610</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>3.045000076293945</v>
+        <v>13.35000038146973</v>
       </c>
       <c r="I29" t="n">
-        <v>9.852216501916431</v>
+        <v>4.344569164245573</v>
       </c>
       <c r="J29" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="K29" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.12</v>
+        <v>0.104</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1835,14 +1835,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>IT0005594418</t>
+          <t>IT0001233417</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>12.55000019073486</v>
+        <v>2.374000072479248</v>
       </c>
       <c r="I30" t="n">
-        <v>0.9561752842728317</v>
+        <v>4.380791778636691</v>
       </c>
       <c r="J30" t="n">
         <v>52</v>
@@ -1854,11 +1854,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1882,14 +1882,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>IT0005453748</t>
+          <t>IT0004056880</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>3.420000076293945</v>
+        <v>9.11400032043457</v>
       </c>
       <c r="I31" t="n">
-        <v>4.970760123029561</v>
+        <v>3.181917816590249</v>
       </c>
       <c r="J31" t="n">
         <v>52</v>
@@ -1901,11 +1901,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.035</v>
+        <v>0.077</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1924,19 +1924,19 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>IT0005378143</t>
+          <t>IT0001469383</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>3.029999971389771</v>
+        <v>1.968000054359436</v>
       </c>
       <c r="I32" t="n">
-        <v>1.155115522458126</v>
+        <v>3.912601517943693</v>
       </c>
       <c r="J32" t="n">
         <v>52</v>
@@ -1948,11 +1948,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.33</v>
+        <v>1.64</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1976,14 +1976,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>IT0005054967</t>
+          <t>IT0000062072</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>5.860000133514404</v>
+        <v>33.52000045776367</v>
       </c>
       <c r="I33" t="n">
-        <v>5.631399189100186</v>
+        <v>4.892601365165419</v>
       </c>
       <c r="J33" t="n">
         <v>52</v>
@@ -1995,11 +1995,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.07000000000000001</v>
+        <v>2</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -2023,14 +2023,14 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>IT0004931496</t>
+          <t>IT0003261697</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>0.9300000071525574</v>
+        <v>32.33000183105469</v>
       </c>
       <c r="I34" t="n">
-        <v>7.526881662541449</v>
+        <v>6.186204413013344</v>
       </c>
       <c r="J34" t="n">
         <v>52</v>
@@ -2042,11 +2042,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.26</v>
+        <v>0.1</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -2070,14 +2070,14 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>IT0003865588</t>
+          <t>NL0015000N33</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>8.699999809265137</v>
+        <v>3.575999975204468</v>
       </c>
       <c r="I35" t="n">
-        <v>2.988505812645086</v>
+        <v>2.796420601045508</v>
       </c>
       <c r="J35" t="n">
         <v>52</v>
@@ -2089,11 +2089,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.35</v>
+        <v>0.14846</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2117,30 +2117,30 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>IT0001006128</t>
+          <t>IT0005119810</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>9.420000076293945</v>
+        <v>32.25</v>
       </c>
       <c r="I36" t="n">
-        <v>3.715498908336511</v>
+        <v>0.4603410852713178</v>
       </c>
       <c r="J36" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="K36" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.096</v>
+        <v>0.92</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -2149,12 +2149,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2164,30 +2164,30 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>IT0005543332</t>
+          <t>IT0003188064</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>4.579999923706055</v>
+        <v>21.84000015258789</v>
       </c>
       <c r="I37" t="n">
-        <v>2.096069903912105</v>
+        <v>4.212454183023375</v>
       </c>
       <c r="J37" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="K37" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -2196,12 +2196,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2211,30 +2211,30 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>IT0005138703</t>
+          <t>NL0015001KT6</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>14.30000019073486</v>
+        <v>8.064999580383301</v>
       </c>
       <c r="I38" t="n">
-        <v>3.496503449866776</v>
+        <v>3.719777006928772</v>
       </c>
       <c r="J38" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="K38" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.08500000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -2243,12 +2243,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2258,30 +2258,30 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>IT0005545238</t>
+          <t>IT0004764699</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>10.10000038146973</v>
+        <v>71.77999877929688</v>
       </c>
       <c r="I39" t="n">
-        <v>0.8415841266298152</v>
+        <v>1.448871576604097</v>
       </c>
       <c r="J39" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="K39" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.095</v>
+        <v>2.2</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -2290,45 +2290,45 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>IT0005466963</t>
+          <t>IT0001031084</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>4.599999904632568</v>
+        <v>50.75</v>
       </c>
       <c r="I40" t="n">
-        <v>2.06521743412054</v>
+        <v>4.334975369458129</v>
       </c>
       <c r="J40" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="K40" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.22</v>
+        <v>0.86</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -2337,12 +2337,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2352,30 +2352,30 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>IT0004171440</t>
+          <t>IT0005508921</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>6.980000019073486</v>
+        <v>7.497000217437744</v>
       </c>
       <c r="I41" t="n">
-        <v>3.15186245557063</v>
+        <v>11.47125483602991</v>
       </c>
       <c r="J41" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="K41" t="n">
-        <v>47</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.16</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -2384,12 +2384,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2399,30 +2399,30 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>IT0004093263</t>
+          <t>IT0000066123</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>3.424999952316284</v>
+        <v>10.86499977111816</v>
       </c>
       <c r="I42" t="n">
-        <v>4.671532911753591</v>
+        <v>5.154164857772179</v>
       </c>
       <c r="J42" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="K42" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>CALTAGIRONE EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.61</v>
+        <v>0.04</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -2431,12 +2431,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2446,30 +2446,30 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>IT0004720733</t>
+          <t>IT0001472171</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>18.92000007629395</v>
+        <v>1.75</v>
       </c>
       <c r="I43" t="n">
-        <v>3.224101466914407</v>
+        <v>2.285714285714286</v>
       </c>
       <c r="J43" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="K43" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -2478,12 +2478,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2493,30 +2493,30 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>IT0001268561</t>
+          <t>IT0003127930</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>11.94999980926514</v>
+        <v>8.539999961853027</v>
       </c>
       <c r="I44" t="n">
-        <v>5.857740679269905</v>
+        <v>3.512880577752431</v>
       </c>
       <c r="J44" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="K44" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5105</v>
+        <v>0.108</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -2525,12 +2525,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2540,44 +2540,44 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>IT0001041000</t>
+          <t>IT0005244618</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>8.569999694824219</v>
+        <v>2.240000009536743</v>
       </c>
       <c r="I45" t="n">
-        <v>5.956826349810867</v>
+        <v>4.821428550901461</v>
       </c>
       <c r="J45" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="K45" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.27</v>
+        <v>2.06</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>DOLLARI USA</t>
+          <t>EURO</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2587,30 +2587,30 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>LU2592315662</t>
+          <t>IT0001128047</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>7.644999980926514</v>
+        <v>64.80000305175781</v>
       </c>
       <c r="I46" t="n">
-        <v>3.531720087293946</v>
+        <v>3.179012195963344</v>
       </c>
       <c r="J46" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="K46" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.35</v>
+        <v>0.75</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2619,12 +2619,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2634,30 +2634,30 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>IT0003850929</t>
+          <t>IT0003121677</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>4.945000171661377</v>
+        <v>14.26000022888184</v>
       </c>
       <c r="I47" t="n">
-        <v>7.07785617492527</v>
+        <v>5.259466956255508</v>
       </c>
       <c r="J47" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="K47" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2681,30 +2681,30 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>IT0005203424</t>
+          <t>NL0013995087</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>38</v>
+        <v>15.10000038146973</v>
       </c>
       <c r="I48" t="n">
-        <v>2.894736842105263</v>
+        <v>1.986754916696235</v>
       </c>
       <c r="J48" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="K48" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2713,45 +2713,45 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Straordinario</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>IT0005252736</t>
+          <t>IT0005246191</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>18.20000076293945</v>
+        <v>40.40000152587891</v>
       </c>
       <c r="I49" t="n">
-        <v>4.120878948132905</v>
+        <v>2.103960316574538</v>
       </c>
       <c r="J49" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="K49" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.43</v>
+        <v>0.85</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2775,30 +2775,30 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>IT0003203947</t>
+          <t>IT0003115950</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>10</v>
+        <v>29.07999992370605</v>
       </c>
       <c r="I50" t="n">
-        <v>4.3</v>
+        <v>2.922971121836486</v>
       </c>
       <c r="J50" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="K50" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.15</v>
+        <v>1.3</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -2807,12 +2807,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2822,30 +2822,30 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>IT0005322612</t>
+          <t>IT0003492391</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>3.845000028610229</v>
+        <v>58.2599983215332</v>
       </c>
       <c r="I51" t="n">
-        <v>3.901170322077145</v>
+        <v>2.23137665199608</v>
       </c>
       <c r="J51" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="K51" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.197169</v>
+        <v>0.6</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2854,12 +2854,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2869,30 +2869,30 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>IT0005455875</t>
+          <t>IT0001463063</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>12.22000026702881</v>
+        <v>6.659999847412109</v>
       </c>
       <c r="I52" t="n">
-        <v>1.613494236428032</v>
+        <v>9.009009215415272</v>
       </c>
       <c r="J52" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="K52" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2901,45 +2901,45 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>IT0005253205</t>
+          <t>IT0005312027</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>26.54999923706055</v>
+        <v>5.449999809265137</v>
       </c>
       <c r="I53" t="n">
-        <v>4.143126296081149</v>
+        <v>3.669724899072381</v>
       </c>
       <c r="J53" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="K53" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.47</v>
+        <v>1</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2948,12 +2948,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2963,30 +2963,30 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>IT0005107492</t>
+          <t>IT0001157020</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>38.20000076293945</v>
+        <v>21.31999969482422</v>
       </c>
       <c r="I54" t="n">
-        <v>1.230366467573426</v>
+        <v>4.690431586838936</v>
       </c>
       <c r="J54" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="K54" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.11</v>
+        <v>0.215</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2995,12 +2995,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3010,30 +3010,30 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>IT0005339160</t>
+          <t>IT0004356751</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>2.380000114440918</v>
+        <v>4.139999866485596</v>
       </c>
       <c r="I55" t="n">
-        <v>4.621848517256896</v>
+        <v>5.193236882456988</v>
       </c>
       <c r="J55" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="K55" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1.2</v>
+        <v>0.24</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -3042,12 +3042,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3057,30 +3057,30 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>IT0005274094</t>
+          <t>IT0004967292</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>75.80000305175781</v>
+        <v>9.329999923706055</v>
       </c>
       <c r="I56" t="n">
-        <v>1.583113392727194</v>
+        <v>2.572347287915811</v>
       </c>
       <c r="J56" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="K56" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.27</v>
+        <v>0.79</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -3089,12 +3089,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3104,30 +3104,30 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>IT0005513202</t>
+          <t>IT0000072170</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>22.39999961853027</v>
+        <v>18.63999938964844</v>
       </c>
       <c r="I57" t="n">
-        <v>1.205357163384253</v>
+        <v>4.238197563669019</v>
       </c>
       <c r="J57" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="K57" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.38</v>
+        <v>0.093</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3151,30 +3151,30 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>IT0001018362</t>
+          <t>IT0005345233</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>10.19999980926514</v>
+        <v>4.485000133514404</v>
       </c>
       <c r="I58" t="n">
-        <v>3.725490265743223</v>
+        <v>2.073578533589163</v>
       </c>
       <c r="J58" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="K58" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -3183,12 +3183,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3198,30 +3198,30 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>IT0005440893</t>
+          <t>IT0001078911</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>26.5</v>
+        <v>32.61999893188477</v>
       </c>
       <c r="I59" t="n">
-        <v>1.132075471698113</v>
+        <v>1.072961408523802</v>
       </c>
       <c r="J59" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="K59" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.007</v>
+        <v>0.06</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3245,30 +3245,30 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>IT0001073045</t>
+          <t>IT0001077780</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>0.1509999930858612</v>
+        <v>1.960000038146973</v>
       </c>
       <c r="I60" t="n">
-        <v>4.635761801670864</v>
+        <v>3.061224430216099</v>
       </c>
       <c r="J60" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="K60" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -3277,12 +3277,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3292,30 +3292,30 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>IT0001033700</t>
+          <t>IT0003411417</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>6.190000057220459</v>
+        <v>11.89999961853027</v>
       </c>
       <c r="I61" t="n">
-        <v>2.584814192584127</v>
+        <v>1.680672322783665</v>
       </c>
       <c r="J61" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="K61" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.065</v>
+        <v>0.103</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3339,30 +3339,30 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>IT0003372205</t>
+          <t>IT0005186371</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>2.200000047683716</v>
+        <v>5.550000190734863</v>
       </c>
       <c r="I62" t="n">
-        <v>2.954545390507408</v>
+        <v>1.855855792076324</v>
       </c>
       <c r="J62" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="K62" t="n">
-        <v>33</v>
+        <v>-311</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.25</v>
+        <v>0.19</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -3371,12 +3371,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3386,30 +3386,30 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>IT0003365613</t>
+          <t>IT0000072618</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>7.28000020980835</v>
+        <v>5.098000049591064</v>
       </c>
       <c r="I63" t="n">
-        <v>3.434065835096747</v>
+        <v>3.72695170952854</v>
       </c>
       <c r="J63" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="K63" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.432</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -3418,12 +3418,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3433,30 +3433,30 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>IT0005549255</t>
+          <t>IT0005211237</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>1.299999952316284</v>
+        <v>9.779999732971191</v>
       </c>
       <c r="I64" t="n">
-        <v>5.384615582121908</v>
+        <v>4.417178034715112</v>
       </c>
       <c r="J64" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="K64" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>3.615</v>
+        <v>0.44</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -3465,12 +3465,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3480,30 +3480,30 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>NL0011585146</t>
+          <t>IT0005541336</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>279.7000122070312</v>
+        <v>24.97999954223633</v>
       </c>
       <c r="I65" t="n">
-        <v>1.292456146667671</v>
+        <v>1.761409159580029</v>
       </c>
       <c r="J65" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="K65" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1.36</v>
+        <v>0.47</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -3512,12 +3512,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3527,30 +3527,30 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>IT0005144784</t>
+          <t>IT0003428445</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>26.29999923706055</v>
+        <v>7.289999961853027</v>
       </c>
       <c r="I66" t="n">
-        <v>5.171102811606022</v>
+        <v>6.447187962406131</v>
       </c>
       <c r="J66" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="K66" t="n">
-        <v>26</v>
+        <v>54</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.585</v>
+        <v>1.4</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -3559,12 +3559,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3574,30 +3574,30 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>IT0004931058</t>
+          <t>IT0004965148</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>13.19999980926514</v>
+        <v>50.13999938964844</v>
       </c>
       <c r="I67" t="n">
-        <v>4.43181824585623</v>
+        <v>2.792181924695105</v>
       </c>
       <c r="J67" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="K67" t="n">
-        <v>26</v>
+        <v>54</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.63</v>
+        <v>0.3</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -3606,12 +3606,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3621,30 +3621,30 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>IT0000062957</t>
+          <t>IT0005366767</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>16.67499923706055</v>
+        <v>2.994999885559082</v>
       </c>
       <c r="I68" t="n">
-        <v>3.778111117389507</v>
+        <v>10.01669487356252</v>
       </c>
       <c r="J68" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="K68" t="n">
-        <v>26</v>
+        <v>54</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.9</v>
+        <v>0.12</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -3653,12 +3653,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3668,67 +3668,2840 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>IT0004176001</t>
+          <t>IT0005594418</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>95.87999725341797</v>
+        <v>11.80000019073486</v>
       </c>
       <c r="I69" t="n">
-        <v>0.9386733685663685</v>
+        <v>1.016949136104436</v>
       </c>
       <c r="J69" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="K69" t="n">
-        <v>26</v>
+        <v>54</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>OMER S.p.A.</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>IT0005453748</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>3.480000019073486</v>
+      </c>
+      <c r="I70" t="n">
+        <v>4.885057444489921</v>
+      </c>
+      <c r="J70" t="n">
+        <v>52</v>
+      </c>
+      <c r="K70" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Pattern S.p.A.</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>IT0005378143</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>3.029999971389771</v>
+      </c>
+      <c r="I71" t="n">
+        <v>1.155115522458126</v>
+      </c>
+      <c r="J71" t="n">
+        <v>52</v>
+      </c>
+      <c r="K71" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>RAI WAY S.p.A.</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>IT0005054967</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>5.78000020980835</v>
+      </c>
+      <c r="I72" t="n">
+        <v>5.709342353310087</v>
+      </c>
+      <c r="J72" t="n">
+        <v>52</v>
+      </c>
+      <c r="K72" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>RCS MediaGroup S.p.A.</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>IT0004931496</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>0.925000011920929</v>
+      </c>
+      <c r="I73" t="n">
+        <v>7.567567470040612</v>
+      </c>
+      <c r="J73" t="n">
+        <v>52</v>
+      </c>
+      <c r="K73" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>RECORDATI S.p.A.</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>IT0003828271</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>48.88000106811523</v>
+      </c>
+      <c r="I74" t="n">
+        <v>1.452536793136729</v>
+      </c>
+      <c r="J74" t="n">
+        <v>52</v>
+      </c>
+      <c r="K74" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>REPLY S.p.A.</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>IT0005282865</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>78.09999847412109</v>
+      </c>
+      <c r="I75" t="n">
+        <v>1.728553170775452</v>
+      </c>
+      <c r="J75" t="n">
+        <v>52</v>
+      </c>
+      <c r="K75" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>SAIPEM S.p.A.</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>IT0005495657</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>3.714999914169312</v>
+      </c>
+      <c r="I76" t="n">
+        <v>4.57604317436472</v>
+      </c>
+      <c r="J76" t="n">
+        <v>52</v>
+      </c>
+      <c r="K76" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>SOL S.p.A.</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>IT0001206769</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>56.20000076293945</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.800711732902232</v>
+      </c>
+      <c r="J77" t="n">
+        <v>52</v>
+      </c>
+      <c r="K77" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>SYS-DAT S.p.A.</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>IT0005595423</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>5</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J78" t="n">
+        <v>52</v>
+      </c>
+      <c r="K78" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Sanlorenzo S.p.A.</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>IT0003549422</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>30.10000038146973</v>
+      </c>
+      <c r="I79" t="n">
+        <v>3.488372048813677</v>
+      </c>
+      <c r="J79" t="n">
+        <v>52</v>
+      </c>
+      <c r="K79" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>TECHNOGYM S.p.A.</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>IT0005162406</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>17.02000045776367</v>
+      </c>
+      <c r="I80" t="n">
+        <v>2.232667390009752</v>
+      </c>
+      <c r="J80" t="n">
+        <v>52</v>
+      </c>
+      <c r="K80" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>TENARIS S.A.</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>DOLLARI USA</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>LU2598331598</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>25.40999984741211</v>
+      </c>
+      <c r="I81" t="n">
+        <v>2.361275102727351</v>
+      </c>
+      <c r="J81" t="n">
+        <v>52</v>
+      </c>
+      <c r="K81" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>IT0001454435</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>28</v>
+      </c>
+      <c r="I82" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J82" t="n">
+        <v>52</v>
+      </c>
+      <c r="K82" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>WEBUILD S.p.A.</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>IT0003865570</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>2.267999887466431</v>
+      </c>
+      <c r="I83" t="n">
+        <v>11.46384536599093</v>
+      </c>
+      <c r="J83" t="n">
+        <v>52</v>
+      </c>
+      <c r="K83" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>IT0001006128</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>9.199999809265137</v>
+      </c>
+      <c r="I84" t="n">
+        <v>3.804347904958889</v>
+      </c>
+      <c r="J84" t="n">
+        <v>45</v>
+      </c>
+      <c r="K84" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Ecomembrane S.p.A.</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>IT0005543332</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>4.599999904632568</v>
+      </c>
+      <c r="I85" t="n">
+        <v>2.086956565006019</v>
+      </c>
+      <c r="J85" t="n">
+        <v>45</v>
+      </c>
+      <c r="K85" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Intred S.p.A.</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Interim</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>IT0005337818</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>8.960000038146973</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0.6696428542918696</v>
+      </c>
+      <c r="J86" t="n">
+        <v>45</v>
+      </c>
+      <c r="K86" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Orsero S.p.A.</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>IT0005138703</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>14.60000038146973</v>
+      </c>
+      <c r="I87" t="n">
+        <v>3.424657444766908</v>
+      </c>
+      <c r="J87" t="n">
+        <v>45</v>
+      </c>
+      <c r="K87" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Porto Aviation Group S.p.A.</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>IT0005545238</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>10.10000038146973</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0.8415841266298152</v>
+      </c>
+      <c r="J88" t="n">
+        <v>45</v>
+      </c>
+      <c r="K88" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Racing Force S.p.A.</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>IT0005466963</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>4.650000095367432</v>
+      </c>
+      <c r="I89" t="n">
+        <v>2.04301071078781</v>
+      </c>
+      <c r="J89" t="n">
+        <v>45</v>
+      </c>
+      <c r="K89" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>ZIGNAGO VETRO S.p.A.</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>IT0004171440</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>7</v>
+      </c>
+      <c r="I90" t="n">
+        <v>3.142857142857143</v>
+      </c>
+      <c r="J90" t="n">
+        <v>45</v>
+      </c>
+      <c r="K90" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>ASCOPIAVE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>IT0004093263</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>3.400000095367432</v>
+      </c>
+      <c r="I91" t="n">
+        <v>4.705882220944735</v>
+      </c>
+      <c r="J91" t="n">
+        <v>38</v>
+      </c>
+      <c r="K91" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Alerion Clean Power S.p.A.</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>IT0004720733</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>18.92000007629395</v>
+      </c>
+      <c r="I92" t="n">
+        <v>3.224101466914407</v>
+      </c>
+      <c r="J92" t="n">
+        <v>38</v>
+      </c>
+      <c r="K92" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>IT0001268561</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="I93" t="n">
+        <v>5.957446808510638</v>
+      </c>
+      <c r="J93" t="n">
+        <v>38</v>
+      </c>
+      <c r="K93" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>0.5105</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>IT0001041000</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>8.470000267028809</v>
+      </c>
+      <c r="I94" t="n">
+        <v>6.027154473503674</v>
+      </c>
+      <c r="J94" t="n">
+        <v>38</v>
+      </c>
+      <c r="K94" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>DOLLARI USA</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>LU2592315662</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>7.409999847412109</v>
+      </c>
+      <c r="I95" t="n">
+        <v>3.643724771388432</v>
+      </c>
+      <c r="J95" t="n">
+        <v>38</v>
+      </c>
+      <c r="K95" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Esprinet S.p.A.</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>IT0003850929</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>4.860000133514404</v>
+      </c>
+      <c r="I96" t="n">
+        <v>7.201645892690646</v>
+      </c>
+      <c r="J96" t="n">
+        <v>38</v>
+      </c>
+      <c r="K96" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>FOPE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>IT0005203424</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>38</v>
+      </c>
+      <c r="I97" t="n">
+        <v>2.894736842105263</v>
+      </c>
+      <c r="J97" t="n">
+        <v>38</v>
+      </c>
+      <c r="K97" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>First Capital S.p.A.</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Straordinario</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>IT0005252736</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>18.60000038146973</v>
+      </c>
+      <c r="I98" t="n">
+        <v>4.032257981818046</v>
+      </c>
+      <c r="J98" t="n">
+        <v>38</v>
+      </c>
+      <c r="K98" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>GEFRAN S.p.A.</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>IT0003203947</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>10.14999961853027</v>
+      </c>
+      <c r="I99" t="n">
+        <v>4.23645336119002</v>
+      </c>
+      <c r="J99" t="n">
+        <v>38</v>
+      </c>
+      <c r="K99" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>IGD SIIQ S.p.A.</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>IT0005322612</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>3.815000057220459</v>
+      </c>
+      <c r="I100" t="n">
+        <v>3.931847909572177</v>
+      </c>
+      <c r="J100" t="n">
+        <v>38</v>
+      </c>
+      <c r="K100" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>INTERCOS S.p.A.</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>0.197169</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>IT0005455875</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>12.27999973297119</v>
+      </c>
+      <c r="I101" t="n">
+        <v>1.605610784099702</v>
+      </c>
+      <c r="J101" t="n">
+        <v>38</v>
+      </c>
+      <c r="K101" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>ITALMOBILIARE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>IT0005253205</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="I102" t="n">
+        <v>4.150943396226416</v>
+      </c>
+      <c r="J102" t="n">
+        <v>38</v>
+      </c>
+      <c r="K102" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>LU-VE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>IT0005107492</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>37.40000152587891</v>
+      </c>
+      <c r="I103" t="n">
+        <v>1.256684440707265</v>
+      </c>
+      <c r="J103" t="n">
+        <v>38</v>
+      </c>
+      <c r="K103" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>PLC S.p.A.</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>IT0005339160</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
+        <v>2.430000066757202</v>
+      </c>
+      <c r="I104" t="n">
+        <v>4.52674884683412</v>
+      </c>
+      <c r="J104" t="n">
+        <v>38</v>
+      </c>
+      <c r="K104" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Pharmanutra S.p.A.</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>IT0005274094</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
+        <v>74.69999694824219</v>
+      </c>
+      <c r="I105" t="n">
+        <v>1.606425768439389</v>
+      </c>
+      <c r="J105" t="n">
+        <v>38</v>
+      </c>
+      <c r="K105" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>REVO Insurance S.p.A.</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>IT0005513202</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>23.20000076293945</v>
+      </c>
+      <c r="I106" t="n">
+        <v>1.163793065176567</v>
+      </c>
+      <c r="J106" t="n">
+        <v>38</v>
+      </c>
+      <c r="K106" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>VALSOIA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>IT0001018362</t>
+        </is>
+      </c>
+      <c r="H107" t="n">
+        <v>10.44999980926514</v>
+      </c>
+      <c r="I107" t="n">
+        <v>3.636363702735056</v>
+      </c>
+      <c r="J107" t="n">
+        <v>38</v>
+      </c>
+      <c r="K107" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>WIIT S.p.A.</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>IT0005440893</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="I108" t="n">
+        <v>1.16504854368932</v>
+      </c>
+      <c r="J108" t="n">
+        <v>38</v>
+      </c>
+      <c r="K108" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Banca Profilo S.p.A.</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>IT0001073045</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>0.1490000039339066</v>
+      </c>
+      <c r="I109" t="n">
+        <v>4.6979864531447</v>
+      </c>
+      <c r="J109" t="n">
+        <v>31</v>
+      </c>
+      <c r="K109" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Basic Net S.p.A.</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>IT0001033700</t>
+        </is>
+      </c>
+      <c r="H110" t="n">
+        <v>6.320000171661377</v>
+      </c>
+      <c r="I110" t="n">
+        <v>2.531645500856685</v>
+      </c>
+      <c r="J110" t="n">
+        <v>31</v>
+      </c>
+      <c r="K110" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>EDISON S.p.A.</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>IT0003372205</t>
+        </is>
+      </c>
+      <c r="H111" t="n">
+        <v>2.255000114440918</v>
+      </c>
+      <c r="I111" t="n">
+        <v>2.882483224002649</v>
+      </c>
+      <c r="J111" t="n">
+        <v>31</v>
+      </c>
+      <c r="K111" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Fiera Milano S.p.A</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>IT0003365613</t>
+        </is>
+      </c>
+      <c r="H112" t="n">
+        <v>7.190000057220459</v>
+      </c>
+      <c r="I112" t="n">
+        <v>3.477051432690058</v>
+      </c>
+      <c r="J112" t="n">
+        <v>31</v>
+      </c>
+      <c r="K112" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>IT0005549255</t>
+        </is>
+      </c>
+      <c r="H113" t="n">
+        <v>1.330000042915344</v>
+      </c>
+      <c r="I113" t="n">
+        <v>5.263157724909606</v>
+      </c>
+      <c r="J113" t="n">
+        <v>31</v>
+      </c>
+      <c r="K113" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Anima Holding S.p.A.</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>IT0004998065</t>
+        </is>
+      </c>
+      <c r="H114" t="n">
+        <v>6.659999847412109</v>
+      </c>
+      <c r="I114" t="n">
+        <v>7.507507679512727</v>
+      </c>
+      <c r="J114" t="n">
+        <v>24</v>
+      </c>
+      <c r="K114" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>IT0004776628</t>
+        </is>
+      </c>
+      <c r="H115" t="n">
+        <v>16.89999961853027</v>
+      </c>
+      <c r="I115" t="n">
+        <v>3.846153932969899</v>
+      </c>
+      <c r="J115" t="n">
+        <v>24</v>
+      </c>
+      <c r="K115" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Banco BPM S.p.A.</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>IT0005218380</t>
+        </is>
+      </c>
+      <c r="H116" t="n">
+        <v>11.67500019073486</v>
+      </c>
+      <c r="I116" t="n">
+        <v>4.625267590389741</v>
+      </c>
+      <c r="J116" t="n">
+        <v>24</v>
+      </c>
+      <c r="K116" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Davide Campari-Milano N.V.</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>NL0015435975</t>
+        </is>
+      </c>
+      <c r="H117" t="n">
+        <v>6.131999969482422</v>
+      </c>
+      <c r="I117" t="n">
+        <v>1.630789310138249</v>
+      </c>
+      <c r="J117" t="n">
+        <v>24</v>
+      </c>
+      <c r="K117" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>IT0005215329</t>
+        </is>
+      </c>
+      <c r="H118" t="n">
+        <v>8.220000267028809</v>
+      </c>
+      <c r="I118" t="n">
+        <v>1.946471956233079</v>
+      </c>
+      <c r="J118" t="n">
+        <v>24</v>
+      </c>
+      <c r="K118" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Ferrari N.V.</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>3.615</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>NL0011585146</t>
+        </is>
+      </c>
+      <c r="H119" t="n">
+        <v>278.2999877929688</v>
+      </c>
+      <c r="I119" t="n">
+        <v>1.298958016013012</v>
+      </c>
+      <c r="J119" t="n">
+        <v>24</v>
+      </c>
+      <c r="K119" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Generalfinance S.p.A.</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>IT0005144784</t>
+        </is>
+      </c>
+      <c r="H120" t="n">
+        <v>26.20000076293945</v>
+      </c>
+      <c r="I120" t="n">
+        <v>5.190839543500142</v>
+      </c>
+      <c r="J120" t="n">
+        <v>24</v>
+      </c>
+      <c r="K120" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>MAIRE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>IT0004931058</t>
+        </is>
+      </c>
+      <c r="H121" t="n">
+        <v>12.97000026702881</v>
+      </c>
+      <c r="I121" t="n">
+        <v>4.510408542451117</v>
+      </c>
+      <c r="J121" t="n">
+        <v>24</v>
+      </c>
+      <c r="K121" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>IT0000062957</t>
+        </is>
+      </c>
+      <c r="H122" t="n">
+        <v>16.68000030517578</v>
+      </c>
+      <c r="I122" t="n">
+        <v>3.776978348162931</v>
+      </c>
+      <c r="J122" t="n">
+        <v>24</v>
+      </c>
+      <c r="K122" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Prysmian S.p.A.</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>IT0004176001</t>
+        </is>
+      </c>
+      <c r="H123" t="n">
+        <v>94.05999755859375</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.9568360869235126</v>
+      </c>
+      <c r="J123" t="n">
+        <v>24</v>
+      </c>
+      <c r="K123" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
           <t>Unicredit S.p.A.</t>
         </is>
       </c>
-      <c r="B70" t="n">
+      <c r="B124" t="n">
         <v>1.7208</v>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E124" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
         <is>
           <t>IT0005239360</t>
         </is>
       </c>
-      <c r="H70" t="n">
-        <v>61.15999984741211</v>
-      </c>
-      <c r="I70" t="n">
-        <v>2.813603669544177</v>
-      </c>
-      <c r="J70" t="n">
+      <c r="H124" t="n">
+        <v>60.22000122070312</v>
+      </c>
+      <c r="I124" t="n">
+        <v>2.857522359877342</v>
+      </c>
+      <c r="J124" t="n">
         <v>24</v>
       </c>
-      <c r="K70" t="n">
+      <c r="K124" t="n">
         <v>26</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>I.CO.P. S.p.A. Società Benefit</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>IT0001214433</t>
+        </is>
+      </c>
+      <c r="H125" t="n">
+        <v>23.39999961853027</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.5982906080440067</v>
+      </c>
+      <c r="J125" t="n">
+        <v>17</v>
+      </c>
+      <c r="K125" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Reti S.p.A.</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>IT0005418204</t>
+        </is>
+      </c>
+      <c r="H126" t="n">
+        <v>1.470000028610229</v>
+      </c>
+      <c r="I126" t="n">
+        <v>4.081632573621466</v>
+      </c>
+      <c r="J126" t="n">
+        <v>17</v>
+      </c>
+      <c r="K126" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Confinvest F.L. S.p.A.</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>IT0005379604</t>
+        </is>
+      </c>
+      <c r="H127" t="n">
+        <v>1.934999942779541</v>
+      </c>
+      <c r="I127" t="n">
+        <v>1.757105995112358</v>
+      </c>
+      <c r="J127" t="n">
+        <v>3</v>
+      </c>
+      <c r="K127" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Eni S.p.A.</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Interim</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>IT0003132476</t>
+        </is>
+      </c>
+      <c r="H128" t="n">
+        <v>23.92499923706055</v>
+      </c>
+      <c r="I128" t="n">
+        <v>1.086729397245924</v>
+      </c>
+      <c r="J128" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K128" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>STMicroelectronics N.V.</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>DOLLARI USA</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Interim</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>NL0000226223</t>
+        </is>
+      </c>
+      <c r="H129" t="n">
+        <v>28.5049991607666</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.3157340910357689</v>
+      </c>
+      <c r="J129" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K129" t="n">
+        <v>-2</v>
       </c>
     </row>
   </sheetData>
@@ -4343,7 +7116,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4360,7 +7133,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4377,7 +7150,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4394,7 +7167,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4411,7 +7184,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4428,7 +7201,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4445,7 +7218,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4462,7 +7235,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4479,7 +7252,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4496,7 +7269,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4513,7 +7286,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4530,7 +7303,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4547,7 +7320,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4564,7 +7337,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4574,14 +7347,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4591,14 +7364,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Annual Preliminary Results</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4615,7 +7388,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4632,7 +7405,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4642,7 +7415,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4683,7 +7456,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4700,7 +7473,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4717,7 +7490,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4734,7 +7507,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4744,14 +7517,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4768,7 +7541,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4778,14 +7551,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4795,14 +7568,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4819,7 +7592,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4938,7 +7711,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4955,7 +7728,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4972,7 +7745,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4982,14 +7755,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5006,7 +7779,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5023,7 +7796,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5033,14 +7806,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5057,7 +7830,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5074,7 +7847,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5091,7 +7864,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5108,7 +7881,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5118,14 +7891,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5135,14 +7908,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5159,7 +7932,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5169,7 +7942,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -5244,7 +8017,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5254,14 +8027,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5295,7 +8068,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -5305,14 +8078,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5329,7 +8102,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -5346,7 +8119,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -5363,7 +8136,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -5373,14 +8146,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -5414,7 +8187,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>NEUROSOFT</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -5431,7 +8204,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -5448,7 +8221,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -5465,7 +8238,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -5475,14 +8248,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -5499,7 +8272,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>NEUROSOFT</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -5516,7 +8289,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -5533,7 +8306,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5543,7 +8316,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -5567,7 +8340,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5577,14 +8350,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5594,7 +8367,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -5703,7 +8476,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5713,14 +8486,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5730,7 +8503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -5764,14 +8537,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5781,14 +8554,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5805,7 +8578,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5815,14 +8588,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>I.CO.P. S.p.A. Società Benefit</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5832,14 +8605,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>I.CO.P. S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5849,7 +8622,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -5890,7 +8663,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>BESTBE HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5907,7 +8680,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5917,14 +8690,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5951,14 +8724,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>BESTBE HOLDING S.p.A.</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5968,14 +8741,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5985,7 +8758,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -6060,7 +8833,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6070,14 +8843,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6087,14 +8860,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -6104,14 +8877,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -6121,14 +8894,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -6138,14 +8911,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Telesia S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -6155,14 +8928,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Telesia S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -6179,7 +8952,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6189,14 +8962,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6213,7 +8986,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6223,14 +8996,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>CULTI Milano S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6240,14 +9013,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6257,14 +9030,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>CULTI Milano S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6274,14 +9047,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6291,14 +9064,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6308,14 +9081,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6332,7 +9105,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -6342,14 +9115,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -6366,7 +9139,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -6376,14 +9149,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -6393,7 +9166,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -6410,14 +9183,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Autostrade Meridionali S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -6427,14 +9200,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -6461,14 +9234,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -6478,14 +9251,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -6502,7 +9275,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Autostrade Meridionali S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -6519,7 +9292,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -6529,14 +9302,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -6546,7 +9319,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -6621,7 +9394,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -6631,14 +9404,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -6655,7 +9428,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -6665,14 +9438,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -6689,7 +9462,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -6699,14 +9472,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -6723,7 +9496,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -6740,7 +9513,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>OVS S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -6757,7 +9530,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -6767,14 +9540,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -6791,7 +9564,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -6801,14 +9574,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>OVS S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -6818,14 +9591,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -6842,7 +9615,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -6852,14 +9625,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -6876,7 +9649,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -6886,14 +9659,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -6903,14 +9676,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -6920,14 +9693,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -6937,14 +9710,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -6954,7 +9727,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -6978,7 +9751,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -6988,14 +9761,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -7005,14 +9778,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -7029,7 +9802,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -7039,14 +9812,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -7056,7 +9829,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -7080,7 +9853,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -7114,7 +9887,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -7131,7 +9904,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -7141,14 +9914,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -7158,7 +9931,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -7182,7 +9955,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>CALTAGIRONE EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -7199,7 +9972,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -7216,7 +9989,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -7233,7 +10006,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>CALTAGIRONE EDITORE S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -7250,7 +10023,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -7260,14 +10033,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -7277,14 +10050,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -7294,14 +10067,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -7318,7 +10091,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>E.P.H. S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -7328,14 +10101,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>E.P.H. S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -7345,7 +10118,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -7369,7 +10142,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -7386,7 +10159,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -7403,7 +10176,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -7420,7 +10193,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -7430,14 +10203,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -7454,7 +10227,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -7471,7 +10244,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -7505,7 +10278,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -7522,7 +10295,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -7532,14 +10305,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -7549,14 +10322,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -7573,7 +10346,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -7583,14 +10356,14 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -7607,7 +10380,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -7617,14 +10390,14 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -7641,7 +10414,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -7651,14 +10424,14 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -7675,7 +10448,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -7692,7 +10465,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -7709,7 +10482,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -7719,14 +10492,14 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Egomnia S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -7760,7 +10533,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -7777,7 +10550,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -7794,7 +10567,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -7811,7 +10584,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -7828,7 +10601,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -7845,7 +10618,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -7862,7 +10635,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -7879,7 +10652,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>gAIn360 S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -7896,7 +10669,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -7913,7 +10686,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -7930,7 +10703,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -7947,7 +10720,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>gAIn360 S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -7964,7 +10737,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -7981,7 +10754,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -7998,7 +10771,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -8015,7 +10788,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -8032,7 +10805,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>Egomnia S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -8049,7 +10822,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -8059,14 +10832,14 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -8083,7 +10856,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -8100,7 +10873,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -8117,7 +10890,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -8134,7 +10907,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -8151,7 +10924,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
+          <t>NEXT RE SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -8161,14 +10934,14 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -8185,7 +10958,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -8202,7 +10975,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -8212,14 +10985,14 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -8236,7 +11009,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>NEXT RE SIIQ S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -8246,14 +11019,14 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -8270,7 +11043,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -8287,7 +11060,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -8297,14 +11070,14 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -8314,14 +11087,14 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -8331,14 +11104,14 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -8355,7 +11128,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -8365,14 +11138,14 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -8389,7 +11162,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -8399,14 +11172,14 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -8423,7 +11196,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -8440,7 +11213,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -8450,7 +11223,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -8523,29 +11296,29 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IT0005337818</t>
+          <t>IT0001463063</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-12-14 00:00:00</t>
+          <t>2026-05-18 00:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>6.659999847412109</v>
       </c>
       <c r="F2" t="n">
-        <v>0.06</v>
+        <v>0.6</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -8553,41 +11326,41 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.6666666666666666</v>
+        <v>9.009009215415272</v>
       </c>
       <c r="I2" t="n">
-        <v>262</v>
+        <v>52</v>
       </c>
       <c r="J2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IT0005594418</t>
+          <t>IT0005561441</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-05-18 00:00:00</t>
+          <t>2026-07-06 00:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>12.55000019073486</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -8595,10 +11368,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.9561752842728317</v>
+        <v>1.75</v>
       </c>
       <c r="I3" t="n">
-        <v>52</v>
+        <v>101</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -8607,12 +11380,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IT0005466963</t>
+          <t>IT0005337818</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -8626,10 +11399,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4.599999904632568</v>
+        <v>8.960000038146973</v>
       </c>
       <c r="F4" t="n">
-        <v>0.095</v>
+        <v>0.06</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -8637,7 +11410,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2.06521743412054</v>
+        <v>0.6696428542918696</v>
       </c>
       <c r="I4" t="n">
         <v>45</v>
@@ -8649,29 +11422,29 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IT0003242622</t>
+          <t>IT0001206769</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-06-22 00:00:00</t>
+          <t>2026-05-18 00:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>9.47599983215332</v>
+        <v>56.20000076293945</v>
       </c>
       <c r="F5" t="n">
-        <v>0.277</v>
+        <v>0.45</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -8679,10 +11452,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2.923174386940177</v>
+        <v>0.800711732902232</v>
       </c>
       <c r="I5" t="n">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -8699,129 +11472,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>BESTBE HOLDING S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>KME Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>S.S. Lazio S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>